--- a/data/trans_bre/P1435_2011_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1435_2011_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215,85%</t>
+          <t>234,03%</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,75</t>
+          <t>0,11; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,86</t>
+          <t>1,89; 7,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,05; 778,97</t>
+          <t>51,9; 943,15</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>523,37%</t>
+          <t>485,12%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,71</t>
+          <t>1,76; 5,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,44</t>
+          <t>3,56; 7,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,2; 1730,01</t>
+          <t>97,03; 2232,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147,28; 1799,79</t>
+          <t>123,34; 1481,48</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368,7%</t>
+          <t>306,17%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,84</t>
+          <t>1,81; 6,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,73</t>
+          <t>3,03; 8,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105,99; 1000,02</t>
+          <t>83,14; 856,14</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1701,24%</t>
+          <t>2440,76%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,05</t>
+          <t>2,92; 8,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,08</t>
+          <t>5,55; 10,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132,18; 2842,05</t>
+          <t>114,73; 3032,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317,57; —</t>
+          <t>560,25; —</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274,64%</t>
+          <t>328,97%</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,38</t>
+          <t>2,36; 8,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,6</t>
+          <t>2,46; 8,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,18; 1213,08</t>
+          <t>20,05; 1509,88</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,51</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>731,28%</t>
+          <t>757,26%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,33</t>
+          <t>0,72; 5,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,34</t>
+          <t>6,75; 12,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>256,09; 2188,77</t>
+          <t>268,9; 2142,02</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,25</t>
+          <t>11,3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1181,65%</t>
+          <t>456,49%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,39</t>
+          <t>2,29; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 65,98</t>
+          <t>8,74; 13,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247,63; —</t>
+          <t>234,96; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286,59; 3833,42</t>
+          <t>205,76; 906,28</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474,58%</t>
+          <t>298,95%</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,34</t>
+          <t>1,29; 3,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,0</t>
+          <t>3,88; 7,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203,24; 1295,6</t>
+          <t>136,35; 606,07</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>748,43%</t>
+          <t>430,31%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,92</t>
+          <t>2,6; 3,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 27,07</t>
+          <t>6,39; 8,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>489,49; 2014,94</t>
+          <t>503,14; 2297,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>375,82; 1948,0</t>
+          <t>295,79; 611,38</t>
         </is>
       </c>
     </row>
